--- a/data/visits/Visits_2026-09-23.xlsx
+++ b/data/visits/Visits_2026-09-23.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -436,16 +436,16 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -577,20 +577,16 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
+      <c r="C2" t="n">
+        <v>3645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Kashan</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>114723</t>
-        </is>
+      <c r="E2" t="n">
+        <v>114723</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -599,7 +595,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-23 08:44:07</t>
+          <t>2026-09-23 8:44:07</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -609,33 +605,145 @@
         <v>67.0336708</v>
       </c>
       <c r="J2" t="n">
-        <v>39.59999847412109</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+        <v>39.59999847</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-23 8:45:05</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>24.8369953</v>
+      </c>
+      <c r="M2" t="n">
+        <v>67.03365549999999</v>
+      </c>
+      <c r="N2" t="n">
+        <v>28.10000038</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0:00:58</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0161</v>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T2" t="n">
         <v>7465.8</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>7467.7</v>
+      </c>
       <c r="V2" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VIS-20260923084848-5CDCEB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3645</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kashan</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>114723</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>STADIUM SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-23 8:48:48</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>24.8370117</v>
+      </c>
+      <c r="I3" t="n">
+        <v>67.0336515</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14.92000008</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:49:50</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>24.8370054</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67.0336516</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12.49699974060059</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>00:01:02</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>7466.4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>7467</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>Mismatch &gt; 1.5 km</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V2"/>
+  <autoFilter ref="A1:V3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>